--- a/data/Phase_1/Data_Dictionary.xlsx
+++ b/data/Phase_1/Data_Dictionary.xlsx
@@ -275,10 +275,10 @@
     <t>amendment_reason</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Reason for an amended version; required when version exceeds 1</t>
+    <t>Conditional</t>
+  </si>
+  <si>
+    <t>Reason for an approved amendment. Required and nonblank when trade_version &gt; 1; null for initial capture. Copied from the amendment request reason.</t>
   </si>
   <si>
     <t>Correct confirmed notional</t>
@@ -864,8 +864,8 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16.285714285714285" customWidth="1"/>
-    <col min="2" max="26" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="23.571428571428573" customWidth="1"/>
+    <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1426,8 +1426,8 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="13.571428571428571" customWidth="1"/>
-    <col min="5" max="5" width="57.57142857142857" customWidth="1"/>
-    <col min="6" max="26" width="13.571428571428571" customWidth="1"/>
+    <col min="5" max="5" width="42.142857142857146" customWidth="1"/>
+    <col min="6" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
